--- a/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04697913466042336</v>
+        <v>0.02809026620502508</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03285177916260074</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07678074167428206</v>
+        <v>0.02809026620502508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04392896251168132</v>
+        <v>0.02809026620502508</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003050172148742036</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0298016070138587</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9232192583257179</v>
+        <v>0.9719097337949749</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
@@ -470,16 +470,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02809026620502508</v>
+        <v>0.05661009097467129</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02809026620502508</v>
+        <v>0.05661009097467129</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02809026620502508</v>
+        <v>0.05661009097467129</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9719097337949749</v>
+        <v>0.9433899090253287</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
@@ -473,22 +473,22 @@
         <v>0.05661009097467129</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.006121295522739989</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05661009097467129</v>
+        <v>0.06824789968536382</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05661009097467129</v>
+        <v>0.06212660416262383</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.005516513187952543</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.01163780871069253</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9433899090253287</v>
+        <v>0.9317521003146362</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05661009097467129</v>
+        <v>0.1297906847152942</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06824789968536382</v>
+        <v>0.2007910274724621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06212660416262383</v>
+        <v>0.05406921447862967</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.005516513187952543</v>
+        <v>0.07572147023666453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01163780871069253</v>
+        <v>0.07100034275716793</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9317521003146362</v>
+        <v>0.7992089725275379</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
@@ -473,10 +473,10 @@
         <v>0.1297906847152942</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2007910274724621</v>
+        <v>0.2007910274724618</v>
       </c>
       <c r="E2" t="n">
         <v>0.05406921447862967</v>
@@ -485,10 +485,10 @@
         <v>0.07572147023666453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07100034275716793</v>
+        <v>0.0710003427571676</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7992089725275379</v>
+        <v>0.7992089725275382</v>
       </c>
     </row>
   </sheetData>
